--- a/tests/testdata/excel/保護/シート保護.xlsx
+++ b/tests/testdata/excel/保護/シート保護.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBD7282B-A341-471E-8C30-048F1496DAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AF710C1-5184-47CB-8897-A092F27A325D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{E348A23B-2AAA-4F2A-A383-9B4EDDEE54BC}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{73AD7F39-7ADE-49FE-ACF4-3D9112D870CF}"/>
   </bookViews>
   <sheets>
     <sheet name="保護シート" sheetId="1" r:id="rId1"/>
@@ -431,7 +431,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8AB9832-7D92-4279-A60A-AF38EB27C37E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BE67467-7F83-4E2C-BA74-18066B008E33}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -444,14 +444,14 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="J+BiZitYuPsmQeCx64duL3qExIGW/JzwdMCwPvyU11Cg2u5bqnMPOUGHkjluUhSJemanZX3KAMFh3iZwwNW3MQ==" saltValue="8hSlnFl+EZccZ6e1MPeoXQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="03c0rLeEB7r1flME9wEKhAWf7nF1WPFBM8Ug04ido08e5mfGdID11xWKXQC55+EVBNjl6R/5am2JhT77u3lL9w==" saltValue="43PgX3Uvx3xw4FhG5QSFfw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3926175B-9779-4EA3-803B-A530055577FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37C9BD22-9997-4264-B1D7-D3C7B8269139}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/保護/シート保護.xlsx
+++ b/tests/testdata/excel/保護/シート保護.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AF710C1-5184-47CB-8897-A092F27A325D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F118654-8FED-47F4-AC4B-3A8E10F47B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{73AD7F39-7ADE-49FE-ACF4-3D9112D870CF}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{ECE3A5E5-0B98-4F30-8C7A-82438E58D3B2}"/>
   </bookViews>
   <sheets>
     <sheet name="保護シート" sheetId="1" r:id="rId1"/>
@@ -431,7 +431,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BE67467-7F83-4E2C-BA74-18066B008E33}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E986E79B-39E5-4C26-9D6D-66CA9C4D7B1A}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -444,14 +444,14 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="03c0rLeEB7r1flME9wEKhAWf7nF1WPFBM8Ug04ido08e5mfGdID11xWKXQC55+EVBNjl6R/5am2JhT77u3lL9w==" saltValue="43PgX3Uvx3xw4FhG5QSFfw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="kDZFbVG93sSoVWQu6Z3H1sahLbLEwb0TEzZ58icXzXpAPD/mC7nOmj/no2HTGbmoeJvZY1JBmVttItbcZQIT9w==" saltValue="E+iIoXzw27k6T13ZhRiLeQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37C9BD22-9997-4264-B1D7-D3C7B8269139}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47200763-D6EF-48E1-BCD3-747E74698BB3}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
